--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4099" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13EF237D-A6D5-4AE4-8980-6828E2996946}"/>
+  <xr:revisionPtr revIDLastSave="4242" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B9CB57B-8B6E-4D5C-9B4F-22659D088C0E}"/>
   <bookViews>
-    <workbookView xWindow="88080" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="88080" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Kiosk Plan" sheetId="5" r:id="rId5"/>
     <sheet name="Temp ME162 open and closings" sheetId="2" r:id="rId6"/>
     <sheet name="Replaced meters" sheetId="10" r:id="rId7"/>
+    <sheet name="Kamstrup handover openings " sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FS Elec'!$A$1:$U$192</definedName>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5138" uniqueCount="1319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5123" uniqueCount="1332">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -4003,6 +4004,45 @@
   </si>
   <si>
     <t>10596203</t>
+  </si>
+  <si>
+    <t>54554256</t>
+  </si>
+  <si>
+    <t>54554258</t>
+  </si>
+  <si>
+    <t>54554254</t>
+  </si>
+  <si>
+    <t>54554253</t>
+  </si>
+  <si>
+    <t>54789028</t>
+  </si>
+  <si>
+    <t>54789025</t>
+  </si>
+  <si>
+    <t>54789029</t>
+  </si>
+  <si>
+    <t>54789031</t>
+  </si>
+  <si>
+    <t>54789026</t>
+  </si>
+  <si>
+    <t>54789020</t>
+  </si>
+  <si>
+    <t>54554259</t>
+  </si>
+  <si>
+    <t>54789024</t>
+  </si>
+  <si>
+    <t>54789022</t>
   </si>
 </sst>
 </file>
@@ -4012,12 +4052,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4466,7 +4513,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -4643,39 +4690,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4686,7 +4747,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -4694,32 +4755,32 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -4727,82 +4788,82 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -4810,99 +4871,99 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="36" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="38" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="39" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
@@ -4912,89 +4973,89 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="42" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="42" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="43" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="43" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="44" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="44" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="45" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="45" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5012,43 +5073,43 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5057,7 +5118,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5072,38 +5133,38 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -5111,23 +5172,34 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Excel Built-in Good" xfId="2" xr:uid="{73A7683C-93AE-4DD2-A667-1D9B92981758}"/>
     <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{EDB79C3E-33DC-4A47-B5C8-E4BE66ABEE17}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{0A8ABF22-C885-4E8B-8CEC-181E323DF71D}"/>
   </cellStyles>
   <dxfs count="35">
     <dxf>
@@ -5821,7 +5893,7 @@
     <col min="10" max="10" width="26.3984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="27.265625" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.59765625" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.3984375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.3984375" bestFit="1" customWidth="1"/>
     <col min="16" max="19" width="11.265625" bestFit="1" customWidth="1"/>
@@ -17677,7 +17749,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U192">
     <sortCondition ref="I2:I192"/>
   </sortState>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="C25:C192 C2:C23">
     <cfRule type="duplicateValues" dxfId="34" priority="8"/>
   </conditionalFormatting>
@@ -17693,26 +17765,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:T204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" customWidth="1"/>
+    <col min="1" max="1" width="30.3984375" customWidth="1"/>
     <col min="2" max="2" width="20.46484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.53125" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
     <col min="4" max="4" width="21.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.73046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.59765625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="31.1328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="39.53125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39.46484375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.86328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27.3984375" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="20.265625" customWidth="1"/>
     <col min="14" max="14" width="35.46484375" customWidth="1"/>
     <col min="15" max="15" width="20.1328125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="24.59765625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.59765625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="22.86328125" customWidth="1"/>
-    <col min="19" max="19" width="11.6640625" customWidth="1"/>
+    <col min="19" max="19" width="11.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.3">
@@ -17774,7 +17847,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>116</v>
       </c>
@@ -17827,7 +17900,7 @@
       <c r="R2" s="136"/>
       <c r="S2" s="136"/>
     </row>
-    <row r="3" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>119</v>
       </c>
@@ -17880,7 +17953,7 @@
       <c r="R3" s="136"/>
       <c r="S3" s="136"/>
     </row>
-    <row r="4" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
         <v>120</v>
       </c>
@@ -17906,7 +17979,7 @@
         <v>46258</v>
       </c>
       <c r="I4" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="63" t="s">
         <v>121</v>
@@ -17933,7 +18006,7 @@
       <c r="R4" s="136"/>
       <c r="S4" s="136"/>
     </row>
-    <row r="5" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
         <v>122</v>
       </c>
@@ -17986,7 +18059,7 @@
       <c r="R5" s="136"/>
       <c r="S5" s="136"/>
     </row>
-    <row r="6" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
         <v>123</v>
       </c>
@@ -18039,7 +18112,7 @@
       <c r="R6" s="136"/>
       <c r="S6" s="136"/>
     </row>
-    <row r="7" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>124</v>
       </c>
@@ -18092,7 +18165,7 @@
       <c r="R7" s="136"/>
       <c r="S7" s="136"/>
     </row>
-    <row r="8" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
         <v>125</v>
       </c>
@@ -18145,7 +18218,7 @@
       <c r="R8" s="136"/>
       <c r="S8" s="136"/>
     </row>
-    <row r="9" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>126</v>
       </c>
@@ -18198,7 +18271,7 @@
       <c r="R9" s="136"/>
       <c r="S9" s="136"/>
     </row>
-    <row r="10" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>127</v>
       </c>
@@ -18251,7 +18324,7 @@
       <c r="R10" s="136"/>
       <c r="S10" s="136"/>
     </row>
-    <row r="11" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
         <v>150</v>
       </c>
@@ -18304,7 +18377,7 @@
       <c r="R11" s="136"/>
       <c r="S11" s="136"/>
     </row>
-    <row r="12" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
         <v>152</v>
       </c>
@@ -18357,7 +18430,7 @@
       <c r="R12" s="136"/>
       <c r="S12" s="136"/>
     </row>
-    <row r="13" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
         <v>153</v>
       </c>
@@ -18410,7 +18483,7 @@
       <c r="R13" s="136"/>
       <c r="S13" s="136"/>
     </row>
-    <row r="14" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
         <v>154</v>
       </c>
@@ -18463,7 +18536,7 @@
       <c r="R14" s="136"/>
       <c r="S14" s="136"/>
     </row>
-    <row r="15" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>155</v>
       </c>
@@ -18516,7 +18589,7 @@
       <c r="R15" s="136"/>
       <c r="S15" s="136"/>
     </row>
-    <row r="16" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
         <v>156</v>
       </c>
@@ -18569,7 +18642,7 @@
       <c r="R16" s="136"/>
       <c r="S16" s="136"/>
     </row>
-    <row r="17" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
         <v>157</v>
       </c>
@@ -18622,7 +18695,7 @@
       <c r="R17" s="136"/>
       <c r="S17" s="136"/>
     </row>
-    <row r="18" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="s">
         <v>158</v>
       </c>
@@ -18675,7 +18748,7 @@
       <c r="R18" s="136"/>
       <c r="S18" s="136"/>
     </row>
-    <row r="19" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
         <v>160</v>
       </c>
@@ -18728,7 +18801,7 @@
       <c r="R19" s="136"/>
       <c r="S19" s="136"/>
     </row>
-    <row r="20" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
         <v>181</v>
       </c>
@@ -18781,7 +18854,7 @@
       <c r="R20" s="136"/>
       <c r="S20" s="136"/>
     </row>
-    <row r="21" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
         <v>183</v>
       </c>
@@ -18834,7 +18907,7 @@
       <c r="R21" s="136"/>
       <c r="S21" s="136"/>
     </row>
-    <row r="22" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
         <v>185</v>
       </c>
@@ -18887,7 +18960,7 @@
       <c r="R22" s="136"/>
       <c r="S22" s="136"/>
     </row>
-    <row r="23" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
         <v>186</v>
       </c>
@@ -18940,7 +19013,7 @@
       <c r="R23" s="136"/>
       <c r="S23" s="136"/>
     </row>
-    <row r="24" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="23" t="s">
         <v>187</v>
       </c>
@@ -18993,7 +19066,7 @@
       <c r="R24" s="136"/>
       <c r="S24" s="136"/>
     </row>
-    <row r="25" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="23" t="s">
         <v>188</v>
       </c>
@@ -19046,7 +19119,7 @@
       <c r="R25" s="136"/>
       <c r="S25" s="136"/>
     </row>
-    <row r="26" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
         <v>203</v>
       </c>
@@ -19099,7 +19172,7 @@
       <c r="R26" s="136"/>
       <c r="S26" s="136"/>
     </row>
-    <row r="27" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="23" t="s">
         <v>205</v>
       </c>
@@ -19152,7 +19225,7 @@
       <c r="R27" s="136"/>
       <c r="S27" s="136"/>
     </row>
-    <row r="28" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="23" t="s">
         <v>206</v>
       </c>
@@ -19205,7 +19278,7 @@
       <c r="R28" s="136"/>
       <c r="S28" s="136"/>
     </row>
-    <row r="29" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
         <v>207</v>
       </c>
@@ -19258,7 +19331,7 @@
       <c r="R29" s="136"/>
       <c r="S29" s="136"/>
     </row>
-    <row r="30" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
         <v>208</v>
       </c>
@@ -19311,7 +19384,7 @@
       <c r="R30" s="136"/>
       <c r="S30" s="136"/>
     </row>
-    <row r="31" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>209</v>
       </c>
@@ -19364,7 +19437,7 @@
       <c r="R31" s="136"/>
       <c r="S31" s="136"/>
     </row>
-    <row r="32" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="23" t="s">
         <v>210</v>
       </c>
@@ -19390,7 +19463,7 @@
         <v>46248</v>
       </c>
       <c r="I32" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="63" t="s">
         <v>159</v>
@@ -19417,7 +19490,7 @@
       <c r="R32" s="136"/>
       <c r="S32" s="136"/>
     </row>
-    <row r="33" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="23" t="s">
         <v>211</v>
       </c>
@@ -19470,7 +19543,7 @@
       <c r="R33" s="136"/>
       <c r="S33" s="136"/>
     </row>
-    <row r="34" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>212</v>
       </c>
@@ -19523,7 +19596,7 @@
       <c r="R34" s="136"/>
       <c r="S34" s="136"/>
     </row>
-    <row r="35" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="23" t="s">
         <v>233</v>
       </c>
@@ -19576,7 +19649,7 @@
       <c r="R35" s="136"/>
       <c r="S35" s="136"/>
     </row>
-    <row r="36" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="23" t="s">
         <v>236</v>
       </c>
@@ -19629,7 +19702,7 @@
       <c r="R36" s="136"/>
       <c r="S36" s="136"/>
     </row>
-    <row r="37" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="23" t="s">
         <v>238</v>
       </c>
@@ -19682,7 +19755,7 @@
       <c r="R37" s="136"/>
       <c r="S37" s="136"/>
     </row>
-    <row r="38" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="23" t="s">
         <v>239</v>
       </c>
@@ -19735,7 +19808,7 @@
       <c r="R38" s="136"/>
       <c r="S38" s="136"/>
     </row>
-    <row r="39" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
         <v>251</v>
       </c>
@@ -19788,7 +19861,7 @@
       <c r="R39" s="136"/>
       <c r="S39" s="136"/>
     </row>
-    <row r="40" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="23" t="s">
         <v>253</v>
       </c>
@@ -19814,7 +19887,7 @@
         <v>46205</v>
       </c>
       <c r="I40" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="63" t="s">
         <v>237</v>
@@ -19843,7 +19916,7 @@
       <c r="R40" s="136"/>
       <c r="S40" s="136"/>
     </row>
-    <row r="41" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="23" t="s">
         <v>254</v>
       </c>
@@ -19896,7 +19969,7 @@
       <c r="R41" s="136"/>
       <c r="S41" s="136"/>
     </row>
-    <row r="42" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="23" t="s">
         <v>255</v>
       </c>
@@ -19949,7 +20022,7 @@
       <c r="R42" s="136"/>
       <c r="S42" s="136"/>
     </row>
-    <row r="43" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="23" t="s">
         <v>256</v>
       </c>
@@ -20002,7 +20075,7 @@
       <c r="R43" s="136"/>
       <c r="S43" s="136"/>
     </row>
-    <row r="44" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="23" t="s">
         <v>257</v>
       </c>
@@ -20055,7 +20128,7 @@
       <c r="R44" s="136"/>
       <c r="S44" s="136"/>
     </row>
-    <row r="45" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="23" t="s">
         <v>258</v>
       </c>
@@ -20108,7 +20181,7 @@
       <c r="R45" s="136"/>
       <c r="S45" s="136"/>
     </row>
-    <row r="46" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="23" t="s">
         <v>259</v>
       </c>
@@ -20134,7 +20207,7 @@
         <v>46205</v>
       </c>
       <c r="I46" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="63" t="s">
         <v>28</v>
@@ -20163,7 +20236,7 @@
       <c r="R46" s="136"/>
       <c r="S46" s="136"/>
     </row>
-    <row r="47" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="s">
         <v>18</v>
       </c>
@@ -20216,7 +20289,7 @@
       <c r="R47" s="136"/>
       <c r="S47" s="136"/>
     </row>
-    <row r="48" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="23" t="s">
         <v>26</v>
       </c>
@@ -20269,7 +20342,7 @@
       <c r="R48" s="136"/>
       <c r="S48" s="136"/>
     </row>
-    <row r="49" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="23" t="s">
         <v>29</v>
       </c>
@@ -20322,7 +20395,7 @@
       <c r="R49" s="136"/>
       <c r="S49" s="136"/>
     </row>
-    <row r="50" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="23" t="s">
         <v>31</v>
       </c>
@@ -20348,7 +20421,7 @@
         <v>46204</v>
       </c>
       <c r="I50" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="63" t="s">
         <v>28</v>
@@ -20377,7 +20450,7 @@
       <c r="R50" s="136"/>
       <c r="S50" s="136"/>
     </row>
-    <row r="51" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="23" t="s">
         <v>32</v>
       </c>
@@ -20430,7 +20503,7 @@
       <c r="R51" s="136"/>
       <c r="S51" s="136"/>
     </row>
-    <row r="52" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
         <v>34</v>
       </c>
@@ -20483,7 +20556,7 @@
       <c r="R52" s="136"/>
       <c r="S52" s="136"/>
     </row>
-    <row r="53" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="23" t="s">
         <v>189</v>
       </c>
@@ -20536,7 +20609,7 @@
       <c r="R53" s="136"/>
       <c r="S53" s="136"/>
     </row>
-    <row r="54" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
         <v>191</v>
       </c>
@@ -20589,7 +20662,7 @@
       <c r="R54" s="136"/>
       <c r="S54" s="136"/>
     </row>
-    <row r="55" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
         <v>192</v>
       </c>
@@ -20642,7 +20715,7 @@
       <c r="R55" s="136"/>
       <c r="S55" s="136"/>
     </row>
-    <row r="56" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="23" t="s">
         <v>193</v>
       </c>
@@ -20695,7 +20768,7 @@
       <c r="R56" s="136"/>
       <c r="S56" s="136"/>
     </row>
-    <row r="57" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="23" t="s">
         <v>194</v>
       </c>
@@ -20748,7 +20821,7 @@
       <c r="R57" s="136"/>
       <c r="S57" s="136"/>
     </row>
-    <row r="58" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
         <v>195</v>
       </c>
@@ -20801,7 +20874,7 @@
       <c r="R58" s="136"/>
       <c r="S58" s="136"/>
     </row>
-    <row r="59" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="23" t="s">
         <v>161</v>
       </c>
@@ -20854,7 +20927,7 @@
       <c r="R59" s="136"/>
       <c r="S59" s="136"/>
     </row>
-    <row r="60" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="23" t="s">
         <v>196</v>
       </c>
@@ -20909,7 +20982,7 @@
       <c r="R60" s="136"/>
       <c r="S60" s="136"/>
     </row>
-    <row r="61" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
         <v>163</v>
       </c>
@@ -20962,7 +21035,7 @@
       <c r="R61" s="136"/>
       <c r="S61" s="136"/>
     </row>
-    <row r="62" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="23" t="s">
         <v>164</v>
       </c>
@@ -21015,7 +21088,7 @@
       <c r="R62" s="136"/>
       <c r="S62" s="136"/>
     </row>
-    <row r="63" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="23" t="s">
         <v>165</v>
       </c>
@@ -21070,7 +21143,7 @@
       <c r="R63" s="136"/>
       <c r="S63" s="136"/>
     </row>
-    <row r="64" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="s">
         <v>166</v>
       </c>
@@ -21123,7 +21196,7 @@
       <c r="R64" s="136"/>
       <c r="S64" s="136"/>
     </row>
-    <row r="65" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
         <v>167</v>
       </c>
@@ -21176,7 +21249,7 @@
       <c r="R65" s="136"/>
       <c r="S65" s="136"/>
     </row>
-    <row r="66" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="23" t="s">
         <v>168</v>
       </c>
@@ -21229,7 +21302,7 @@
       <c r="R66" s="136"/>
       <c r="S66" s="136"/>
     </row>
-    <row r="67" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="23" t="s">
         <v>169</v>
       </c>
@@ -21282,7 +21355,7 @@
       <c r="R67" s="136"/>
       <c r="S67" s="136"/>
     </row>
-    <row r="68" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="23" t="s">
         <v>170</v>
       </c>
@@ -21337,7 +21410,7 @@
       <c r="R68" s="136"/>
       <c r="S68" s="136"/>
     </row>
-    <row r="69" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="23" t="s">
         <v>128</v>
       </c>
@@ -21390,7 +21463,7 @@
       <c r="R69" s="136"/>
       <c r="S69" s="136"/>
     </row>
-    <row r="70" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="23" t="s">
         <v>131</v>
       </c>
@@ -21443,7 +21516,7 @@
       <c r="R70" s="136"/>
       <c r="S70" s="136"/>
     </row>
-    <row r="71" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
         <v>133</v>
       </c>
@@ -21496,7 +21569,7 @@
       <c r="R71" s="136"/>
       <c r="S71" s="136"/>
     </row>
-    <row r="72" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="23" t="s">
         <v>134</v>
       </c>
@@ -21549,7 +21622,7 @@
       <c r="R72" s="136"/>
       <c r="S72" s="136"/>
     </row>
-    <row r="73" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="23" t="s">
         <v>135</v>
       </c>
@@ -21604,7 +21677,7 @@
       <c r="R73" s="136"/>
       <c r="S73" s="136"/>
     </row>
-    <row r="74" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="23" t="s">
         <v>136</v>
       </c>
@@ -21657,7 +21730,7 @@
       <c r="R74" s="136"/>
       <c r="S74" s="136"/>
     </row>
-    <row r="75" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="23" t="s">
         <v>137</v>
       </c>
@@ -21710,7 +21783,7 @@
       <c r="R75" s="136"/>
       <c r="S75" s="136"/>
     </row>
-    <row r="76" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="23" t="s">
         <v>138</v>
       </c>
@@ -21763,7 +21836,7 @@
       <c r="R76" s="136"/>
       <c r="S76" s="136"/>
     </row>
-    <row r="77" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="23" t="s">
         <v>96</v>
       </c>
@@ -21822,7 +21895,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="23" t="s">
         <v>99</v>
       </c>
@@ -21879,7 +21952,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="23" t="s">
         <v>100</v>
       </c>
@@ -21936,7 +22009,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="23" t="s">
         <v>101</v>
       </c>
@@ -21993,7 +22066,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="23" t="s">
         <v>240</v>
       </c>
@@ -22050,7 +22123,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="23" t="s">
         <v>243</v>
       </c>
@@ -22076,7 +22149,7 @@
         <v>46171</v>
       </c>
       <c r="I82" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" s="63" t="s">
         <v>242</v>
@@ -22109,7 +22182,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="23" t="s">
         <v>244</v>
       </c>
@@ -22166,7 +22239,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="23" t="s">
         <v>245</v>
       </c>
@@ -22223,7 +22296,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="23" t="s">
         <v>246</v>
       </c>
@@ -22280,7 +22353,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="23" t="s">
         <v>247</v>
       </c>
@@ -22337,7 +22410,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="23" t="s">
         <v>248</v>
       </c>
@@ -22394,7 +22467,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="23" t="s">
         <v>249</v>
       </c>
@@ -22451,7 +22524,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="23" t="s">
         <v>250</v>
       </c>
@@ -22508,7 +22581,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="23" t="s">
         <v>228</v>
       </c>
@@ -22565,7 +22638,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="23" t="s">
         <v>231</v>
       </c>
@@ -22622,7 +22695,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="23" t="s">
         <v>232</v>
       </c>
@@ -22679,7 +22752,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="23" t="s">
         <v>197</v>
       </c>
@@ -22705,7 +22778,7 @@
         <v>46161</v>
       </c>
       <c r="I93" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" s="63" t="s">
         <v>98</v>
@@ -22738,7 +22811,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="23" t="s">
         <v>199</v>
       </c>
@@ -22795,7 +22868,7 @@
         <v>11.769</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="21.4" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" s="23" t="s">
         <v>200</v>
       </c>
@@ -22857,7 +22930,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="23" t="s">
         <v>201</v>
       </c>
@@ -22914,7 +22987,7 @@
         <v>2.952</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="23" t="s">
         <v>202</v>
       </c>
@@ -22973,7 +23046,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="23" t="s">
         <v>171</v>
       </c>
@@ -23030,7 +23103,7 @@
         <v>32.673999999999999</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="23" t="s">
         <v>173</v>
       </c>
@@ -23087,7 +23160,7 @@
         <v>4.1719999999999997</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="23" t="s">
         <v>175</v>
       </c>
@@ -23144,7 +23217,7 @@
         <v>4.3360000000000003</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
         <v>176</v>
       </c>
@@ -23201,7 +23274,7 @@
         <v>4.3209</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="23" t="s">
         <v>177</v>
       </c>
@@ -23258,7 +23331,7 @@
         <v>9.7119999999999997</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="23" t="s">
         <v>178</v>
       </c>
@@ -23315,7 +23388,7 @@
         <v>4.1757999999999997</v>
       </c>
     </row>
-    <row r="104" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="23" t="s">
         <v>179</v>
       </c>
@@ -23374,14 +23447,16 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
         <v>139</v>
       </c>
       <c r="B105" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C105" s="53"/>
+      <c r="C105" s="53" t="s">
+        <v>1305</v>
+      </c>
       <c r="D105" s="53" t="s">
         <v>284</v>
       </c>
@@ -23391,10 +23466,14 @@
       <c r="F105" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
+      <c r="G105" s="3">
+        <v>1.2929999999999999</v>
+      </c>
+      <c r="H105" s="57">
+        <v>46293</v>
+      </c>
       <c r="I105" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="63" t="s">
         <v>107</v>
@@ -23421,7 +23500,7 @@
       <c r="R105" s="136"/>
       <c r="S105" s="136"/>
     </row>
-    <row r="106" spans="1:20" ht="21.4" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106" s="23" t="s">
         <v>180</v>
       </c>
@@ -23483,25 +23562,31 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="23" t="s">
         <v>141</v>
       </c>
       <c r="B107" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C107" s="53"/>
+      <c r="C107" s="53" t="s">
+        <v>1320</v>
+      </c>
       <c r="D107" s="53" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="E107" s="53" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="F107" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G107" s="3"/>
-      <c r="H107" s="3"/>
+      <c r="G107" s="3">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="H107" s="57">
+        <v>46293</v>
+      </c>
       <c r="I107" s="21" t="b">
         <v>0</v>
       </c>
@@ -23530,7 +23615,7 @@
       <c r="R107" s="136"/>
       <c r="S107" s="136"/>
     </row>
-    <row r="108" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
         <v>142</v>
       </c>
@@ -23587,25 +23672,31 @@
         <v>20.81</v>
       </c>
     </row>
-    <row r="109" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
         <v>144</v>
       </c>
       <c r="B109" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C109" s="53"/>
+      <c r="C109" s="53" t="s">
+        <v>1321</v>
+      </c>
       <c r="D109" s="53" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="E109" s="53" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="F109" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
+      <c r="G109" s="3">
+        <v>0.184</v>
+      </c>
+      <c r="H109" s="57">
+        <v>46293</v>
+      </c>
       <c r="I109" s="21" t="b">
         <v>0</v>
       </c>
@@ -23634,7 +23725,7 @@
       <c r="R109" s="136"/>
       <c r="S109" s="136"/>
     </row>
-    <row r="110" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="23" t="s">
         <v>145</v>
       </c>
@@ -23693,25 +23784,31 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
         <v>146</v>
       </c>
       <c r="B111" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C111" s="53"/>
+      <c r="C111" s="53" t="s">
+        <v>1322</v>
+      </c>
       <c r="D111" s="53" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="E111" s="53" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="F111" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
+      <c r="G111" s="3">
+        <v>0.184</v>
+      </c>
+      <c r="H111" s="57">
+        <v>46293</v>
+      </c>
       <c r="I111" s="21" t="b">
         <v>0</v>
       </c>
@@ -23740,7 +23837,7 @@
       <c r="R111" s="136"/>
       <c r="S111" s="136"/>
     </row>
-    <row r="112" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:20" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
         <v>147</v>
       </c>
@@ -23797,25 +23894,31 @@
         <v>8.8550000000000004</v>
       </c>
     </row>
-    <row r="113" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="23" t="s">
         <v>105</v>
       </c>
       <c r="B113" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C113" s="53"/>
+      <c r="C113" s="53" t="s">
+        <v>1323</v>
+      </c>
       <c r="D113" s="53" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="E113" s="53" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="F113" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
+      <c r="G113" s="3">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="H113" s="156">
+        <v>46293</v>
+      </c>
       <c r="I113" s="21" t="b">
         <v>0</v>
       </c>
@@ -23844,7 +23947,7 @@
       <c r="R113" s="136"/>
       <c r="S113" s="136"/>
     </row>
-    <row r="114" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="23" t="s">
         <v>148</v>
       </c>
@@ -23901,25 +24004,31 @@
         <v>6.4509999999999996</v>
       </c>
     </row>
-    <row r="115" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="s">
         <v>108</v>
       </c>
       <c r="B115" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C115" s="53"/>
+      <c r="C115" s="53" t="s">
+        <v>1324</v>
+      </c>
       <c r="D115" s="53" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="E115" s="53" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="F115" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
+      <c r="G115" s="3">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="H115" s="156">
+        <v>46293</v>
+      </c>
       <c r="I115" s="21" t="b">
         <v>0</v>
       </c>
@@ -23948,7 +24057,7 @@
       <c r="R115" s="136"/>
       <c r="S115" s="136"/>
     </row>
-    <row r="116" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="23" t="s">
         <v>149</v>
       </c>
@@ -24005,25 +24114,31 @@
         <v>4.7329999999999997</v>
       </c>
     </row>
-    <row r="117" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="s">
         <v>109</v>
       </c>
       <c r="B117" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C117" s="53"/>
+      <c r="C117" s="53" t="s">
+        <v>1325</v>
+      </c>
       <c r="D117" s="53" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="E117" s="53" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="F117" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
+      <c r="G117" s="3">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="H117" s="156">
+        <v>46293</v>
+      </c>
       <c r="I117" s="21" t="b">
         <v>0</v>
       </c>
@@ -24052,7 +24167,7 @@
       <c r="R117" s="136"/>
       <c r="S117" s="136"/>
     </row>
-    <row r="118" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="23" t="s">
         <v>110</v>
       </c>
@@ -24109,14 +24224,16 @@
         <v>20.442</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="s">
         <v>111</v>
       </c>
       <c r="B119" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C119" s="53"/>
+      <c r="C119" s="53" t="s">
+        <v>1303</v>
+      </c>
       <c r="D119" s="53" t="s">
         <v>284</v>
       </c>
@@ -24126,10 +24243,14 @@
       <c r="F119" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
+      <c r="G119" s="3">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="H119" s="156">
+        <v>46293</v>
+      </c>
       <c r="I119" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" s="63" t="s">
         <v>107</v>
@@ -24156,7 +24277,7 @@
       <c r="R119" s="136"/>
       <c r="S119" s="136"/>
     </row>
-    <row r="120" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="s">
         <v>112</v>
       </c>
@@ -24213,25 +24334,31 @@
         <v>0.223</v>
       </c>
     </row>
-    <row r="121" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="23" t="s">
         <v>113</v>
       </c>
       <c r="B121" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C121" s="53"/>
+      <c r="C121" s="53" t="s">
+        <v>1326</v>
+      </c>
       <c r="D121" s="53" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="E121" s="53" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="F121" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G121" s="3"/>
-      <c r="H121" s="3"/>
+      <c r="G121" s="3">
+        <v>1.093</v>
+      </c>
+      <c r="H121" s="156">
+        <v>46293</v>
+      </c>
       <c r="I121" s="21" t="b">
         <v>0</v>
       </c>
@@ -24260,7 +24387,7 @@
       <c r="R121" s="136"/>
       <c r="S121" s="136"/>
     </row>
-    <row r="122" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="s">
         <v>114</v>
       </c>
@@ -24317,25 +24444,31 @@
         <v>7.593</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="23" t="s">
         <v>74</v>
       </c>
       <c r="B123" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C123" s="53"/>
+      <c r="C123" s="53" t="s">
+        <v>1319</v>
+      </c>
       <c r="D123" s="53" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="E123" s="53" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="F123" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G123" s="3"/>
-      <c r="H123" s="3"/>
+      <c r="G123" s="3">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="H123" s="57">
+        <v>46293</v>
+      </c>
       <c r="I123" s="21" t="b">
         <v>0</v>
       </c>
@@ -24364,7 +24497,7 @@
       <c r="R123" s="136"/>
       <c r="S123" s="136"/>
     </row>
-    <row r="124" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="23" t="s">
         <v>115</v>
       </c>
@@ -24421,25 +24554,31 @@
         <v>3.8929999999999998</v>
       </c>
     </row>
-    <row r="125" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="23" t="s">
         <v>77</v>
       </c>
       <c r="B125" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C125" s="53"/>
+      <c r="C125" s="53" t="s">
+        <v>1327</v>
+      </c>
       <c r="D125" s="53" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="E125" s="53" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="F125" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G125" s="3"/>
-      <c r="H125" s="3"/>
+      <c r="G125" s="3">
+        <v>0.308</v>
+      </c>
+      <c r="H125" s="156">
+        <v>46293</v>
+      </c>
       <c r="I125" s="21" t="b">
         <v>0</v>
       </c>
@@ -24468,7 +24607,7 @@
       <c r="R125" s="136"/>
       <c r="S125" s="136"/>
     </row>
-    <row r="126" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="23" t="s">
         <v>78</v>
       </c>
@@ -24535,17 +24674,13 @@
         <v>27</v>
       </c>
       <c r="C127" s="53"/>
-      <c r="D127" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E127" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="D127" s="53"/>
+      <c r="E127" s="53"/>
       <c r="F127" s="53" t="s">
         <v>286</v>
       </c>
       <c r="G127" s="3"/>
-      <c r="H127" s="3"/>
+      <c r="H127" s="156"/>
       <c r="I127" s="21" t="b">
         <v>0</v>
       </c>
@@ -24574,7 +24709,7 @@
       <c r="R127" s="136"/>
       <c r="S127" s="136"/>
     </row>
-    <row r="128" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="23" t="s">
         <v>82</v>
       </c>
@@ -24631,25 +24766,31 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="129" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="23" t="s">
         <v>83</v>
       </c>
       <c r="B129" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C129" s="53"/>
+      <c r="C129" s="53" t="s">
+        <v>1329</v>
+      </c>
       <c r="D129" s="53" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="E129" s="53" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="F129" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G129" s="3"/>
-      <c r="H129" s="3"/>
+      <c r="G129" s="3">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="H129" s="156">
+        <v>46293</v>
+      </c>
       <c r="I129" s="21" t="b">
         <v>0</v>
       </c>
@@ -24678,25 +24819,31 @@
       <c r="R129" s="136"/>
       <c r="S129" s="136"/>
     </row>
-    <row r="130" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="23" t="s">
         <v>84</v>
       </c>
       <c r="B130" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C130" s="53"/>
+      <c r="C130" s="53" t="s">
+        <v>1328</v>
+      </c>
       <c r="D130" s="53" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="E130" s="53" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="F130" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G130" s="3"/>
-      <c r="H130" s="3"/>
+      <c r="G130" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="H130" s="156">
+        <v>46293</v>
+      </c>
       <c r="I130" s="21" t="b">
         <v>0</v>
       </c>
@@ -24725,25 +24872,31 @@
       <c r="R130" s="136"/>
       <c r="S130" s="136"/>
     </row>
-    <row r="131" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="23" t="s">
         <v>85</v>
       </c>
       <c r="B131" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C131" s="53"/>
+      <c r="C131" s="53" t="s">
+        <v>1330</v>
+      </c>
       <c r="D131" s="53" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="E131" s="53" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="F131" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G131" s="3"/>
-      <c r="H131" s="3"/>
+      <c r="G131" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="H131" s="156">
+        <v>46293</v>
+      </c>
       <c r="I131" s="21" t="b">
         <v>0</v>
       </c>
@@ -24772,25 +24925,31 @@
       <c r="R131" s="136"/>
       <c r="S131" s="136"/>
     </row>
-    <row r="132" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="23" t="s">
         <v>86</v>
       </c>
       <c r="B132" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C132" s="53"/>
+      <c r="C132" s="53" t="s">
+        <v>1331</v>
+      </c>
       <c r="D132" s="53" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="E132" s="53" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="F132" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G132" s="3"/>
-      <c r="H132" s="3"/>
+      <c r="G132" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="H132" s="156">
+        <v>46293</v>
+      </c>
       <c r="I132" s="21" t="b">
         <v>0</v>
       </c>
@@ -24827,12 +24986,8 @@
         <v>27</v>
       </c>
       <c r="C133" s="53"/>
-      <c r="D133" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E133" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="D133" s="53"/>
+      <c r="E133" s="53"/>
       <c r="F133" s="53" t="s">
         <v>286</v>
       </c>
@@ -24874,12 +25029,8 @@
         <v>27</v>
       </c>
       <c r="C134" s="53"/>
-      <c r="D134" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E134" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="D134" s="53"/>
+      <c r="E134" s="53"/>
       <c r="F134" s="53" t="s">
         <v>286</v>
       </c>
@@ -24921,12 +25072,8 @@
         <v>27</v>
       </c>
       <c r="C135" s="53"/>
-      <c r="D135" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E135" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="D135" s="53"/>
+      <c r="E135" s="53"/>
       <c r="F135" s="53" t="s">
         <v>286</v>
       </c>
@@ -24968,12 +25115,8 @@
         <v>27</v>
       </c>
       <c r="C136" s="53"/>
-      <c r="D136" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E136" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="D136" s="53"/>
+      <c r="E136" s="53"/>
       <c r="F136" s="53" t="s">
         <v>286</v>
       </c>
@@ -25015,12 +25158,8 @@
         <v>27</v>
       </c>
       <c r="C137" s="53"/>
-      <c r="D137" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E137" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="D137" s="53"/>
+      <c r="E137" s="53"/>
       <c r="F137" s="53" t="s">
         <v>286</v>
       </c>
@@ -25062,12 +25201,8 @@
         <v>27</v>
       </c>
       <c r="C138" s="53"/>
-      <c r="D138" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E138" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="D138" s="53"/>
+      <c r="E138" s="53"/>
       <c r="F138" s="53" t="s">
         <v>286</v>
       </c>
@@ -25109,12 +25244,8 @@
         <v>27</v>
       </c>
       <c r="C139" s="53"/>
-      <c r="D139" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E139" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="D139" s="53"/>
+      <c r="E139" s="53"/>
       <c r="F139" s="53" t="s">
         <v>286</v>
       </c>
@@ -25156,12 +25287,8 @@
         <v>27</v>
       </c>
       <c r="C140" s="53"/>
-      <c r="D140" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E140" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="D140" s="53"/>
+      <c r="E140" s="53"/>
       <c r="F140" s="53" t="s">
         <v>286</v>
       </c>
@@ -25202,14 +25329,10 @@
       <c r="B141" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C141" s="53"/>
-      <c r="D141" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E141" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="F141" s="53" t="s">
+      <c r="C141" s="154"/>
+      <c r="D141" s="53"/>
+      <c r="E141" s="53"/>
+      <c r="F141" s="155" t="s">
         <v>286</v>
       </c>
       <c r="G141" s="3"/>
@@ -25242,7 +25365,7 @@
       <c r="R141" s="136"/>
       <c r="S141" s="136"/>
     </row>
-    <row r="142" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="23" t="s">
         <v>38</v>
       </c>
@@ -25268,7 +25391,7 @@
         <v>46258</v>
       </c>
       <c r="I142" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142" s="63" t="s">
         <v>39</v>
@@ -25302,10 +25425,12 @@
       <c r="B143" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C143" s="53"/>
+      <c r="C143" s="154"/>
       <c r="D143" s="53"/>
       <c r="E143" s="53"/>
-      <c r="F143" s="53"/>
+      <c r="F143" s="155" t="s">
+        <v>286</v>
+      </c>
       <c r="G143" s="3"/>
       <c r="H143" s="57"/>
       <c r="I143" s="21" t="b">
@@ -25336,7 +25461,7 @@
       <c r="R143" s="136"/>
       <c r="S143" s="136"/>
     </row>
-    <row r="144" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="23" t="s">
         <v>41</v>
       </c>
@@ -25362,7 +25487,7 @@
         <v>46258</v>
       </c>
       <c r="I144" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" s="63" t="s">
         <v>39</v>
@@ -25396,6 +25521,14 @@
       <c r="B145" s="60" t="s">
         <v>27</v>
       </c>
+      <c r="C145" s="159"/>
+      <c r="D145" s="17"/>
+      <c r="E145" s="17"/>
+      <c r="F145" s="155" t="s">
+        <v>286</v>
+      </c>
+      <c r="G145" s="17"/>
+      <c r="H145" s="17"/>
       <c r="I145" s="21" t="b">
         <v>0</v>
       </c>
@@ -25424,7 +25557,7 @@
       <c r="R145" s="136"/>
       <c r="S145" s="136"/>
     </row>
-    <row r="146" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="23" t="s">
         <v>43</v>
       </c>
@@ -25450,7 +25583,7 @@
         <v>46258</v>
       </c>
       <c r="I146" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" s="63" t="s">
         <v>39</v>
@@ -25477,7 +25610,7 @@
       <c r="R146" s="136"/>
       <c r="S146" s="136"/>
     </row>
-    <row r="147" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="23" t="s">
         <v>45</v>
       </c>
@@ -25503,7 +25636,7 @@
         <v>46258</v>
       </c>
       <c r="I147" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147" s="63" t="s">
         <v>37</v>
@@ -25537,13 +25670,9 @@
       <c r="B148" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C148" s="53"/>
-      <c r="D148" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E148" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="C148" s="154"/>
+      <c r="D148" s="53"/>
+      <c r="E148" s="53"/>
       <c r="F148" s="53" t="s">
         <v>286</v>
       </c>
@@ -25577,7 +25706,7 @@
       <c r="R148" s="136"/>
       <c r="S148" s="136"/>
     </row>
-    <row r="149" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="23" t="s">
         <v>47</v>
       </c>
@@ -25603,7 +25732,7 @@
         <v>46258</v>
       </c>
       <c r="I149" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J149" s="63" t="s">
         <v>37</v>
@@ -25637,13 +25766,9 @@
       <c r="B150" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C150" s="53"/>
-      <c r="D150" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E150" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="C150" s="154"/>
+      <c r="D150" s="53"/>
+      <c r="E150" s="53"/>
       <c r="F150" s="53" t="s">
         <v>286</v>
       </c>
@@ -25677,7 +25802,7 @@
       <c r="R150" s="136"/>
       <c r="S150" s="136"/>
     </row>
-    <row r="151" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="23" t="s">
         <v>49</v>
       </c>
@@ -25703,7 +25828,7 @@
         <v>46258</v>
       </c>
       <c r="I151" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151" s="63" t="s">
         <v>37</v>
@@ -25738,12 +25863,8 @@
         <v>19</v>
       </c>
       <c r="C152" s="53"/>
-      <c r="D152" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E152" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="D152" s="53"/>
+      <c r="E152" s="53"/>
       <c r="F152" s="53" t="s">
         <v>286</v>
       </c>
@@ -25777,7 +25898,7 @@
       <c r="R152" s="136"/>
       <c r="S152" s="136"/>
     </row>
-    <row r="153" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="23" t="s">
         <v>51</v>
       </c>
@@ -25803,7 +25924,7 @@
         <v>46258</v>
       </c>
       <c r="I153" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" s="63" t="s">
         <v>37</v>
@@ -25838,12 +25959,8 @@
         <v>19</v>
       </c>
       <c r="C154" s="53"/>
-      <c r="D154" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E154" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="D154" s="53"/>
+      <c r="E154" s="53"/>
       <c r="F154" s="53" t="s">
         <v>286</v>
       </c>
@@ -25885,12 +26002,8 @@
         <v>19</v>
       </c>
       <c r="C155" s="53"/>
-      <c r="D155" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E155" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="D155" s="53"/>
+      <c r="E155" s="53"/>
       <c r="F155" s="53" t="s">
         <v>286</v>
       </c>
@@ -25924,7 +26037,7 @@
       <c r="R155" s="136"/>
       <c r="S155" s="136"/>
     </row>
-    <row r="156" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="23" t="s">
         <v>54</v>
       </c>
@@ -25977,7 +26090,7 @@
       <c r="R156" s="136"/>
       <c r="S156" s="136"/>
     </row>
-    <row r="157" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="23" t="s">
         <v>57</v>
       </c>
@@ -26030,7 +26143,7 @@
       <c r="R157" s="136"/>
       <c r="S157" s="136"/>
     </row>
-    <row r="158" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="23" t="s">
         <v>58</v>
       </c>
@@ -26083,7 +26196,7 @@
       <c r="R158" s="136"/>
       <c r="S158" s="136"/>
     </row>
-    <row r="159" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="23" t="s">
         <v>59</v>
       </c>
@@ -26136,7 +26249,7 @@
       <c r="R159" s="136"/>
       <c r="S159" s="136"/>
     </row>
-    <row r="160" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="23" t="s">
         <v>60</v>
       </c>
@@ -26189,7 +26302,7 @@
       <c r="R160" s="136"/>
       <c r="S160" s="136"/>
     </row>
-    <row r="161" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="23" t="s">
         <v>61</v>
       </c>
@@ -26242,7 +26355,7 @@
       <c r="R161" s="136"/>
       <c r="S161" s="136"/>
     </row>
-    <row r="162" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="23" t="s">
         <v>62</v>
       </c>
@@ -26295,7 +26408,7 @@
       <c r="R162" s="136"/>
       <c r="S162" s="136"/>
     </row>
-    <row r="163" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="23" t="s">
         <v>63</v>
       </c>
@@ -26348,7 +26461,7 @@
       <c r="R163" s="136"/>
       <c r="S163" s="136"/>
     </row>
-    <row r="164" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="23" t="s">
         <v>87</v>
       </c>
@@ -26401,7 +26514,7 @@
       <c r="R164" s="136"/>
       <c r="S164" s="136"/>
     </row>
-    <row r="165" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="23" t="s">
         <v>90</v>
       </c>
@@ -26454,7 +26567,7 @@
       <c r="R165" s="136"/>
       <c r="S165" s="136"/>
     </row>
-    <row r="166" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="23" t="s">
         <v>91</v>
       </c>
@@ -26507,7 +26620,7 @@
       <c r="R166" s="136"/>
       <c r="S166" s="136"/>
     </row>
-    <row r="167" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="23" t="s">
         <v>92</v>
       </c>
@@ -26560,7 +26673,7 @@
       <c r="R167" s="136"/>
       <c r="S167" s="136"/>
     </row>
-    <row r="168" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="23" t="s">
         <v>93</v>
       </c>
@@ -26613,7 +26726,7 @@
       <c r="R168" s="136"/>
       <c r="S168" s="136"/>
     </row>
-    <row r="169" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="23" t="s">
         <v>94</v>
       </c>
@@ -26674,12 +26787,8 @@
         <v>19</v>
       </c>
       <c r="C170" s="53"/>
-      <c r="D170" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E170" s="53" t="s">
-        <v>285</v>
-      </c>
+      <c r="D170" s="53"/>
+      <c r="E170" s="53"/>
       <c r="F170" s="53" t="s">
         <v>286</v>
       </c>
@@ -26713,7 +26822,7 @@
       <c r="R170" s="136"/>
       <c r="S170" s="136"/>
     </row>
-    <row r="171" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="23" t="s">
         <v>220</v>
       </c>
@@ -26766,7 +26875,7 @@
       <c r="R171" s="136"/>
       <c r="S171" s="136"/>
     </row>
-    <row r="172" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="23" t="s">
         <v>223</v>
       </c>
@@ -26819,7 +26928,7 @@
       <c r="R172" s="136"/>
       <c r="S172" s="136"/>
     </row>
-    <row r="173" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="23" t="s">
         <v>224</v>
       </c>
@@ -26872,7 +26981,7 @@
       <c r="R173" s="136"/>
       <c r="S173" s="136"/>
     </row>
-    <row r="174" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="23" t="s">
         <v>225</v>
       </c>
@@ -26925,7 +27034,7 @@
       <c r="R174" s="136"/>
       <c r="S174" s="136"/>
     </row>
-    <row r="175" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="23" t="s">
         <v>226</v>
       </c>
@@ -26978,7 +27087,7 @@
       <c r="R175" s="136"/>
       <c r="S175" s="136"/>
     </row>
-    <row r="176" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="23" t="s">
         <v>227</v>
       </c>
@@ -27031,7 +27140,7 @@
       <c r="R176" s="136"/>
       <c r="S176" s="136"/>
     </row>
-    <row r="177" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="23" t="s">
         <v>213</v>
       </c>
@@ -27084,7 +27193,7 @@
       <c r="R177" s="136"/>
       <c r="S177" s="136"/>
     </row>
-    <row r="178" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="23" t="s">
         <v>215</v>
       </c>
@@ -27137,7 +27246,7 @@
       <c r="R178" s="136"/>
       <c r="S178" s="136"/>
     </row>
-    <row r="179" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="23" t="s">
         <v>216</v>
       </c>
@@ -27190,7 +27299,7 @@
       <c r="R179" s="136"/>
       <c r="S179" s="136"/>
     </row>
-    <row r="180" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="23" t="s">
         <v>217</v>
       </c>
@@ -27243,7 +27352,7 @@
       <c r="R180" s="136"/>
       <c r="S180" s="136"/>
     </row>
-    <row r="181" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="23" t="s">
         <v>218</v>
       </c>
@@ -27296,7 +27405,7 @@
       <c r="R181" s="136"/>
       <c r="S181" s="136"/>
     </row>
-    <row r="182" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="23" t="s">
         <v>219</v>
       </c>
@@ -27349,7 +27458,7 @@
       <c r="R182" s="136"/>
       <c r="S182" s="136"/>
     </row>
-    <row r="183" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="23" t="s">
         <v>64</v>
       </c>
@@ -27402,7 +27511,7 @@
       <c r="R183" s="136"/>
       <c r="S183" s="136"/>
     </row>
-    <row r="184" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="23" t="s">
         <v>68</v>
       </c>
@@ -27428,7 +27537,7 @@
         <v>46186</v>
       </c>
       <c r="I184" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J184" s="63" t="s">
         <v>69</v>
@@ -27457,7 +27566,7 @@
       <c r="R184" s="136"/>
       <c r="S184" s="136"/>
     </row>
-    <row r="185" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="23" t="s">
         <v>70</v>
       </c>
@@ -27510,7 +27619,7 @@
       <c r="R185" s="136"/>
       <c r="S185" s="136"/>
     </row>
-    <row r="186" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="23" t="s">
         <v>71</v>
       </c>
@@ -27536,7 +27645,7 @@
         <v>46186</v>
       </c>
       <c r="I186" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J186" s="63" t="s">
         <v>69</v>
@@ -27565,7 +27674,7 @@
       <c r="R186" s="136"/>
       <c r="S186" s="136"/>
     </row>
-    <row r="187" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="23" t="s">
         <v>72</v>
       </c>
@@ -27620,7 +27729,7 @@
       <c r="R187" s="136"/>
       <c r="S187" s="136"/>
     </row>
-    <row r="188" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="23" t="s">
         <v>73</v>
       </c>
@@ -27675,7 +27784,7 @@
       <c r="R188" s="136"/>
       <c r="S188" s="136"/>
     </row>
-    <row r="189" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="23" t="s">
         <v>102</v>
       </c>
@@ -27730,7 +27839,7 @@
       <c r="R189" s="136"/>
       <c r="S189" s="136"/>
     </row>
-    <row r="190" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="23" t="s">
         <v>103</v>
       </c>
@@ -27783,7 +27892,7 @@
       <c r="R190" s="136"/>
       <c r="S190" s="136"/>
     </row>
-    <row r="191" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="23" t="s">
         <v>104</v>
       </c>
@@ -27836,7 +27945,7 @@
       <c r="R191" s="136"/>
       <c r="S191" s="136"/>
     </row>
-    <row r="192" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>365</v>
       </c>
@@ -27889,7 +27998,7 @@
       <c r="R192" s="136"/>
       <c r="S192" s="136"/>
     </row>
-    <row r="193" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>368</v>
       </c>
@@ -27946,10 +28055,15 @@
       <c r="Q204" s="57"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N193">
+  <autoFilter ref="A1:T193" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T193">
     <sortCondition ref="A2:A193"/>
   </sortState>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="C2:C3 C5:C63">
     <cfRule type="duplicateValues" dxfId="31" priority="2"/>
     <cfRule type="duplicateValues" dxfId="30" priority="5"/>
@@ -38003,34 +38117,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="157" t="s">
         <v>1164</v>
       </c>
-      <c r="B1" s="154" t="s">
+      <c r="B1" s="157" t="s">
         <v>1165</v>
       </c>
-      <c r="C1" s="154" t="s">
+      <c r="C1" s="157" t="s">
         <v>1166</v>
       </c>
-      <c r="D1" s="155" t="s">
+      <c r="D1" s="158" t="s">
         <v>1167</v>
       </c>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155" t="s">
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158" t="s">
         <v>1168</v>
       </c>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
       <c r="J1" s="108"/>
       <c r="K1" s="109" t="s">
         <v>1169</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A2" s="154"/>
-      <c r="B2" s="154"/>
-      <c r="C2" s="154"/>
+      <c r="A2" s="157"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
       <c r="D2" s="107" t="s">
         <v>1170</v>
       </c>
@@ -39144,7 +39258,7 @@
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="G1:I1"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -40537,13 +40651,13 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.53125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.53125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.9296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.46484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.86328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.06640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.1328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.3984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -41282,4 +41396,13 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34554505-D33C-4080-B013-8BA5742BB9F7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4277" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8BA02EC-B27E-4DAB-8A4A-7A36ABB01727}"/>
+  <xr:revisionPtr revIDLastSave="4314" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A21BD7F9-D0A2-4495-AD3E-7444FDE1190E}"/>
   <bookViews>
-    <workbookView xWindow="59280" yWindow="-2430" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FS Elec'!$A$1:$U$192</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FS Water'!$A$1:$T$193</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5123" uniqueCount="1332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5128" uniqueCount="1333">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -4043,6 +4043,9 @@
   </si>
   <si>
     <t>54789022</t>
+  </si>
+  <si>
+    <t>probe removed</t>
   </si>
 </sst>
 </file>
@@ -4710,7 +4713,7 @@
     <xf numFmtId="0" fontId="20" fillId="37" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5184,16 +5187,22 @@
     <xf numFmtId="14" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5203,7 +5212,87 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{0A8ABF22-C885-4E8B-8CEC-181E323DF71D}"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="43">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5896,7 +5985,7 @@
     <col min="11" max="11" width="27.265625" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.59765625" customWidth="1"/>
     <col min="13" max="13" width="18.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.1328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.3984375" bestFit="1" customWidth="1"/>
     <col min="16" max="19" width="11.265625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16.86328125" bestFit="1" customWidth="1"/>
@@ -7317,7 +7406,7 @@
       <c r="B24" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="158">
+      <c r="C24" s="156">
         <v>14558068921</v>
       </c>
       <c r="D24" s="2">
@@ -9730,7 +9819,7 @@
         <v>1286</v>
       </c>
       <c r="N63" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O63" s="64" t="s">
         <v>130</v>
@@ -9785,12 +9874,12 @@
         <v>46197</v>
       </c>
       <c r="L64" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="N64" s="7">
+      <c r="N64" s="159">
         <v>2</v>
       </c>
       <c r="O64" s="64" t="s">
@@ -10940,7 +11029,7 @@
       <c r="B83" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C83" s="158">
+      <c r="C83" s="156">
         <v>14558069077</v>
       </c>
       <c r="D83" s="2">
@@ -13850,7 +13939,7 @@
       <c r="M128" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="N128" s="159">
+      <c r="N128" s="2">
         <v>7</v>
       </c>
       <c r="O128" s="64" t="s">
@@ -14098,7 +14187,7 @@
       <c r="M132" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="N132" s="159">
+      <c r="N132" s="2">
         <v>1</v>
       </c>
       <c r="O132" s="64" t="s">
@@ -15347,8 +15436,8 @@
       <c r="M153" s="2" t="s">
         <v>1288</v>
       </c>
-      <c r="N153" s="7">
-        <v>8</v>
+      <c r="N153" s="7" t="s">
+        <v>1332</v>
       </c>
       <c r="O153" s="64" t="s">
         <v>37</v>
@@ -15652,7 +15741,7 @@
       <c r="M158" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="N158" s="159">
+      <c r="N158" s="2">
         <v>2</v>
       </c>
       <c r="O158" s="64" t="s">
@@ -15713,7 +15802,7 @@
       <c r="M159" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="N159" s="159">
+      <c r="N159" s="2">
         <v>3</v>
       </c>
       <c r="O159" s="64" t="s">
@@ -15774,7 +15863,7 @@
       <c r="M160" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="N160" s="159">
+      <c r="N160" s="2">
         <v>8</v>
       </c>
       <c r="O160" s="64" t="s">
@@ -15835,7 +15924,7 @@
       <c r="M161" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="N161" s="159">
+      <c r="N161" s="2">
         <v>4</v>
       </c>
       <c r="O161" s="64" t="s">
@@ -15896,7 +15985,7 @@
       <c r="M162" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="N162" s="159">
+      <c r="N162" s="2">
         <v>5</v>
       </c>
       <c r="O162" s="64" t="s">
@@ -15957,7 +16046,7 @@
       <c r="M163" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="N163" s="159">
+      <c r="N163" s="2">
         <v>6</v>
       </c>
       <c r="O163" s="64" t="s">
@@ -16018,7 +16107,7 @@
       <c r="M164" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="N164" s="159">
+      <c r="N164" s="2">
         <v>6</v>
       </c>
       <c r="O164" s="64" t="s">
@@ -16079,7 +16168,7 @@
       <c r="M165" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="N165" s="159">
+      <c r="N165" s="2">
         <v>3</v>
       </c>
       <c r="O165" s="64" t="s">
@@ -16140,7 +16229,7 @@
       <c r="M166" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="N166" s="159">
+      <c r="N166" s="2">
         <v>2</v>
       </c>
       <c r="O166" s="64" t="s">
@@ -16201,7 +16290,7 @@
       <c r="M167" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="N167" s="159">
+      <c r="N167" s="2">
         <v>1</v>
       </c>
       <c r="O167" s="64" t="s">
@@ -16262,7 +16351,7 @@
       <c r="M168" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="N168" s="159">
+      <c r="N168" s="2">
         <v>5</v>
       </c>
       <c r="O168" s="64" t="s">
@@ -16323,7 +16412,7 @@
       <c r="M169" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="N169" s="159">
+      <c r="N169" s="2">
         <v>7</v>
       </c>
       <c r="O169" s="64" t="s">
@@ -16384,7 +16473,7 @@
       <c r="M170" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="N170" s="159">
+      <c r="N170" s="2">
         <v>4</v>
       </c>
       <c r="O170" s="64" t="s">
@@ -16445,7 +16534,7 @@
       <c r="M171" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N171" s="159">
+      <c r="N171" s="2">
         <v>1</v>
       </c>
       <c r="O171" s="64" t="s">
@@ -16506,7 +16595,7 @@
       <c r="M172" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N172" s="159">
+      <c r="N172" s="2">
         <v>2</v>
       </c>
       <c r="O172" s="64" t="s">
@@ -16567,7 +16656,7 @@
       <c r="M173" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N173" s="159">
+      <c r="N173" s="2">
         <v>3</v>
       </c>
       <c r="O173" s="64" t="s">
@@ -16628,7 +16717,7 @@
       <c r="M174" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N174" s="159">
+      <c r="N174" s="2">
         <v>4</v>
       </c>
       <c r="O174" s="64" t="s">
@@ -16689,7 +16778,7 @@
       <c r="M175" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N175" s="159">
+      <c r="N175" s="2">
         <v>5</v>
       </c>
       <c r="O175" s="64" t="s">
@@ -16750,7 +16839,7 @@
       <c r="M176" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N176" s="159">
+      <c r="N176" s="2">
         <v>6</v>
       </c>
       <c r="O176" s="64" t="s">
@@ -16811,7 +16900,7 @@
       <c r="M177" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="N177" s="159">
+      <c r="N177" s="2">
         <v>1</v>
       </c>
       <c r="O177" s="64" t="s">
@@ -17753,13 +17842,13 @@
   </sortState>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="C25:C192 C2:C23">
-    <cfRule type="duplicateValues" dxfId="34" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C117:C122">
-    <cfRule type="duplicateValues" dxfId="33" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C124:C132">
-    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21043,8 +21132,8 @@
       <c r="B62" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C62" s="53" t="s">
-        <v>314</v>
+      <c r="C62" s="160">
+        <v>10852211</v>
       </c>
       <c r="D62" s="53" t="s">
         <v>284</v>
@@ -21062,7 +21151,7 @@
         <v>46186</v>
       </c>
       <c r="I62" s="21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="63" t="s">
         <v>132</v>
@@ -21080,12 +21169,14 @@
         <v>46179</v>
       </c>
       <c r="O62" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P62" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="Q62" s="57">
+        <v>46318</v>
+      </c>
       <c r="R62" s="136"/>
       <c r="S62" s="136"/>
     </row>
@@ -21471,8 +21562,8 @@
       <c r="B70" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C70" s="53" t="s">
-        <v>320</v>
+      <c r="C70" s="160">
+        <v>10852373</v>
       </c>
       <c r="D70" s="53" t="s">
         <v>284</v>
@@ -21490,7 +21581,7 @@
         <v>46186</v>
       </c>
       <c r="I70" s="21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" s="63" t="s">
         <v>132</v>
@@ -21508,12 +21599,14 @@
         <v>46179</v>
       </c>
       <c r="O70" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P70" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="Q70" s="57">
+        <v>46318</v>
+      </c>
       <c r="R70" s="136"/>
       <c r="S70" s="136"/>
     </row>
@@ -28059,11 +28152,11 @@
     <sortCondition ref="A2:A193"/>
   </sortState>
   <phoneticPr fontId="11" type="noConversion"/>
-  <conditionalFormatting sqref="C2:C3 C5:C63">
-    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
+  <conditionalFormatting sqref="C2:C3 C5:C61 C63">
+    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="11"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -33785,7 +33878,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C143:C268">
-    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -38072,22 +38165,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:D125">
-    <cfRule type="duplicateValues" dxfId="26" priority="6" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="6" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C126:D251">
-    <cfRule type="duplicateValues" dxfId="25" priority="5" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="5" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E126:E251">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"Maybe"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38112,34 +38205,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="157" t="s">
         <v>1164</v>
       </c>
-      <c r="B1" s="156" t="s">
+      <c r="B1" s="157" t="s">
         <v>1165</v>
       </c>
-      <c r="C1" s="156" t="s">
+      <c r="C1" s="157" t="s">
         <v>1166</v>
       </c>
-      <c r="D1" s="157" t="s">
+      <c r="D1" s="158" t="s">
         <v>1167</v>
       </c>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157" t="s">
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158" t="s">
         <v>1168</v>
       </c>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
       <c r="J1" s="108"/>
       <c r="K1" s="109" t="s">
         <v>1169</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A2" s="156"/>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
+      <c r="A2" s="157"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
       <c r="D2" s="107" t="s">
         <v>1170</v>
       </c>
@@ -40642,7 +40735,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8F51D9-DC2A-407D-9B2E-297FBBC4C6A6}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -41352,42 +41445,106 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
+    <row r="25" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>314</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D25" s="3">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="E25" s="57">
+        <v>46186</v>
+      </c>
+      <c r="F25" s="150" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" s="57">
+        <v>46318</v>
+      </c>
+      <c r="H25" s="160">
+        <v>10852211</v>
+      </c>
+      <c r="I25" s="161">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" s="53" t="s">
+        <v>320</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D26" s="3">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="E26" s="57">
+        <v>46186</v>
+      </c>
+      <c r="F26" s="150" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" s="57">
+        <v>46318</v>
+      </c>
+      <c r="H26" s="160">
+        <v>10852373</v>
+      </c>
+      <c r="I26" s="161">
+        <v>8.5000000000000006E-2</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I15">
     <sortCondition ref="G2:G15"/>
   </sortState>
   <conditionalFormatting sqref="A2:A16 A19:A22 A24">
-    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2">
+    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
     <cfRule type="duplicateValues" dxfId="7" priority="1"/>
     <cfRule type="duplicateValues" dxfId="6" priority="2"/>
     <cfRule type="duplicateValues" dxfId="5" priority="3"/>
     <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
-    <cfRule type="duplicateValues" dxfId="3" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
